--- a/bin/doctor.xlsx
+++ b/bin/doctor.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -579,15 +579,15 @@
       </c>
       <c r="E2" t="str">
         <f ca="1">VLOOKUP(F2,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Family Medicine</v>
+        <v>Obstetrics and Gynecology</v>
       </c>
       <c r="F2">
         <f ca="1">ROUNDUP(RAND()*5,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="str">
         <f ca="1">CONCATENATE("(",B2,", ", CHAR(39), C2, CHAR(39), ", ", CHAR(39), D2, CHAR(39), ", ", CHAR(39),  E2, CHAR(39), "),")</f>
-        <v>(1907, 'Mannix', 'Owen', 'Family Medicine'),</v>
+        <v>(1907, 'Mannix', 'Owen', 'Obstetrics and Gynecology'),</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -631,15 +631,15 @@
       </c>
       <c r="E4" t="str">
         <f ca="1">VLOOKUP(F4,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Pediatrics</v>
+        <v>Obstetrics and Gynecology</v>
       </c>
       <c r="F4">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(350, 'Cameran', 'Howe', 'Pediatrics'),</v>
+        <v>(350, 'Cameran', 'Howe', 'Obstetrics and Gynecology'),</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -657,15 +657,15 @@
       </c>
       <c r="E5" t="str">
         <f ca="1">VLOOKUP(F5,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Obstetrics and Gynecology</v>
+        <v>Internal Medicine</v>
       </c>
       <c r="F5">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1050, 'Iris', 'Burch', 'Obstetrics and Gynecology'),</v>
+        <v>(1050, 'Iris', 'Burch', 'Internal Medicine'),</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -709,15 +709,15 @@
       </c>
       <c r="E7" t="str">
         <f ca="1">VLOOKUP(F7,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Family Medicine</v>
+        <v>Pediatrics</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1698, 'Logan', 'Terry', 'Family Medicine'),</v>
+        <v>(1698, 'Logan', 'Terry', 'Pediatrics'),</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -761,15 +761,15 @@
       </c>
       <c r="E9" t="str">
         <f ca="1">VLOOKUP(F9,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Pediatrics</v>
+        <v>Obstetrics and Gynecology</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1429, 'Grace', 'Henry', 'Pediatrics'),</v>
+        <v>(1429, 'Grace', 'Henry', 'Obstetrics and Gynecology'),</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -787,15 +787,15 @@
       </c>
       <c r="E10" t="str">
         <f ca="1">VLOOKUP(F10,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Psychiatry</v>
+        <v>Family Medicine</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(284, 'Iris', 'Beasley', 'Psychiatry'),</v>
+        <v>(284, 'Iris', 'Beasley', 'Family Medicine'),</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -813,15 +813,15 @@
       </c>
       <c r="E11" t="str">
         <f ca="1">VLOOKUP(F11,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Family Medicine</v>
+        <v>Internal Medicine</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(617, 'Tasha', 'Dickson', 'Family Medicine'),</v>
+        <v>(617, 'Tasha', 'Dickson', 'Internal Medicine'),</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -839,15 +839,15 @@
       </c>
       <c r="E12" t="str">
         <f ca="1">VLOOKUP(F12,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Pediatrics</v>
+        <v>Internal Medicine</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(542, 'Clarke', 'Montgomery', 'Pediatrics'),</v>
+        <v>(542, 'Clarke', 'Montgomery', 'Internal Medicine'),</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -865,15 +865,15 @@
       </c>
       <c r="E13" t="str">
         <f ca="1">VLOOKUP(F13,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Family Medicine</v>
+        <v>Obstetrics and Gynecology</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(863, 'Meghan', 'Sanders', 'Family Medicine'),</v>
+        <v>(863, 'Meghan', 'Sanders', 'Obstetrics and Gynecology'),</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -891,15 +891,15 @@
       </c>
       <c r="E14" t="str">
         <f ca="1">VLOOKUP(F14,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Psychiatry</v>
+        <v>Obstetrics and Gynecology</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1165, 'Ramona', 'Todd', 'Psychiatry'),</v>
+        <v>(1165, 'Ramona', 'Todd', 'Obstetrics and Gynecology'),</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -917,15 +917,15 @@
       </c>
       <c r="E15" t="str">
         <f ca="1">VLOOKUP(F15,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Family Medicine</v>
+        <v>Obstetrics and Gynecology</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1625, 'Knox', 'Jefferson', 'Family Medicine'),</v>
+        <v>(1625, 'Knox', 'Jefferson', 'Obstetrics and Gynecology'),</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -943,15 +943,15 @@
       </c>
       <c r="E16" t="str">
         <f ca="1">VLOOKUP(F16,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Internal Medicine</v>
+        <v>Family Medicine</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(470, 'Jada', 'Leblanc', 'Internal Medicine'),</v>
+        <v>(470, 'Jada', 'Leblanc', 'Family Medicine'),</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -969,15 +969,15 @@
       </c>
       <c r="E17" t="str">
         <f ca="1">VLOOKUP(F17,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Psychiatry</v>
+        <v>Family Medicine</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1819, 'Nina', 'Kerr', 'Psychiatry'),</v>
+        <v>(1819, 'Nina', 'Kerr', 'Family Medicine'),</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1021,15 +1021,15 @@
       </c>
       <c r="E19" t="str">
         <f ca="1">VLOOKUP(F19,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Family Medicine</v>
+        <v>Psychiatry</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1169, 'Alvin', 'Wolf', 'Family Medicine'),</v>
+        <v>(1169, 'Alvin', 'Wolf', 'Psychiatry'),</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1047,15 +1047,15 @@
       </c>
       <c r="E20" t="str">
         <f ca="1">VLOOKUP(F20,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Pediatrics</v>
+        <v>Internal Medicine</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1558, 'Tana', 'Herrera', 'Pediatrics'),</v>
+        <v>(1558, 'Tana', 'Herrera', 'Internal Medicine'),</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="E21" t="str">
         <f ca="1">VLOOKUP(F21,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Family Medicine</v>
+        <v>Pediatrics</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(191, 'Margaret', 'Day', 'Family Medicine'),</v>
+        <v>(191, 'Margaret', 'Day', 'Pediatrics'),</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="E22" t="str">
         <f ca="1">VLOOKUP(F22,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Pediatrics</v>
+        <v>Obstetrics and Gynecology</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1, 'Holmes', 'Vincent', 'Pediatrics'),</v>
+        <v>(1, 'Holmes', 'Vincent', 'Obstetrics and Gynecology'),</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1125,15 +1125,15 @@
       </c>
       <c r="E23" t="str">
         <f ca="1">VLOOKUP(F23,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Obstetrics and Gynecology</v>
+        <v>Pediatrics</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(56, 'Chester', 'Rasmussen', 'Obstetrics and Gynecology'),</v>
+        <v>(56, 'Chester', 'Rasmussen', 'Pediatrics'),</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1151,15 +1151,15 @@
       </c>
       <c r="E24" t="str">
         <f ca="1">VLOOKUP(F24,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Obstetrics and Gynecology</v>
+        <v>Pediatrics</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1188, 'Graiden', 'Reeves', 'Obstetrics and Gynecology'),</v>
+        <v>(1188, 'Graiden', 'Reeves', 'Pediatrics'),</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1177,15 +1177,15 @@
       </c>
       <c r="E25" t="str">
         <f ca="1">VLOOKUP(F25,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Pediatrics</v>
+        <v>Family Medicine</v>
       </c>
       <c r="F25">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(1953, 'Walter', 'Avila', 'Pediatrics'),</v>
+        <v>(1953, 'Walter', 'Avila', 'Family Medicine'),</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1203,15 +1203,15 @@
       </c>
       <c r="E26" t="str">
         <f ca="1">VLOOKUP(F26,speciality!$A$2:$B$6,2,FALSE)</f>
-        <v>Pediatrics</v>
+        <v>Family Medicine</v>
       </c>
       <c r="F26">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>(377, 'Tara', 'Stafford', 'Pediatrics'),</v>
+        <v>(377, 'Tara', 'Stafford', 'Family Medicine'),</v>
       </c>
     </row>
   </sheetData>
